--- a/artfynd/A 36807-2025 artfynd.xlsx
+++ b/artfynd/A 36807-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119934467</v>
+        <v>119934261</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754901</v>
+        <v>754888</v>
       </c>
       <c r="R2" t="n">
-        <v>7234127</v>
+        <v>7233830</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,57 +775,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119934357</v>
+        <v>119934219</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754863</v>
+        <v>754821</v>
       </c>
       <c r="R3" t="n">
-        <v>7234125</v>
+        <v>7233880</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,44 +882,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119934336</v>
+        <v>119934204</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755044</v>
+        <v>755015</v>
       </c>
       <c r="R4" t="n">
-        <v>7233662</v>
+        <v>7233693</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,50 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119934644</v>
+        <v>119933999</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754960</v>
+        <v>755017</v>
       </c>
       <c r="R5" t="n">
-        <v>7233931</v>
+        <v>7233763</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1081,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,49 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119934332</v>
+        <v>119934002</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755002</v>
+        <v>754955</v>
       </c>
       <c r="R6" t="n">
-        <v>7233709</v>
+        <v>7233873</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,12 +1213,7 @@
         <v>119934003</v>
       </c>
       <c r="B7" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119934581</v>
+        <v>119934007</v>
       </c>
       <c r="B8" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754935</v>
+        <v>755018</v>
       </c>
       <c r="R8" t="n">
-        <v>7234162</v>
+        <v>7233903</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,62 +1412,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119934334</v>
+        <v>119934008</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>755032</v>
+        <v>754781</v>
       </c>
       <c r="R9" t="n">
-        <v>7233670</v>
+        <v>7234011</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1529,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,44 +1524,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119934360</v>
+        <v>119934077</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>754927</v>
+        <v>754977</v>
       </c>
       <c r="R10" t="n">
-        <v>7234172</v>
+        <v>7233937</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,50 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119934333</v>
+        <v>119934535</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>755006</v>
+        <v>754839</v>
       </c>
       <c r="R11" t="n">
-        <v>7233705</v>
+        <v>7233912</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1753,22 +1703,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,27 +1733,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119934163</v>
+        <v>119934183</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>755023</v>
+        <v>754960</v>
       </c>
       <c r="R12" t="n">
-        <v>7233776</v>
+        <v>7233858</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,50 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119934355</v>
+        <v>119934160</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Grundvattnet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>754788</v>
+        <v>755201</v>
       </c>
       <c r="R13" t="n">
-        <v>7233985</v>
+        <v>7233658</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1977,22 +1917,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2012,57 +1952,52 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119934645</v>
+        <v>119934163</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>754862</v>
+        <v>755023</v>
       </c>
       <c r="R14" t="n">
-        <v>7234127</v>
+        <v>7233776</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2089,22 +2024,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,27 +2054,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119933999</v>
+        <v>119934165</v>
       </c>
       <c r="B15" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>755017</v>
+        <v>755005</v>
       </c>
       <c r="R15" t="n">
-        <v>7233763</v>
+        <v>7233743</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,50 +2173,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119934049</v>
+        <v>119934168</v>
       </c>
       <c r="B16" t="n">
-        <v>90084</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>754837</v>
+        <v>755008</v>
       </c>
       <c r="R16" t="n">
-        <v>7233966</v>
+        <v>7233852</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2313,22 +2238,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,57 +2273,52 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119934261</v>
+        <v>119934578</v>
       </c>
       <c r="B17" t="n">
-        <v>90825</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>754888</v>
+        <v>755012</v>
       </c>
       <c r="R17" t="n">
-        <v>7233830</v>
+        <v>7233916</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2425,22 +2345,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,49 +2375,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119934643</v>
+        <v>119934580</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>754977</v>
+        <v>754811</v>
       </c>
       <c r="R18" t="n">
-        <v>7233943</v>
+        <v>7234002</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119934580</v>
+        <v>119934581</v>
       </c>
       <c r="B19" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>754811</v>
+        <v>754935</v>
       </c>
       <c r="R19" t="n">
-        <v>7234002</v>
+        <v>7234162</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119934468</v>
+        <v>119934415</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,14 +2632,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>754926</v>
+        <v>755030</v>
       </c>
       <c r="R20" t="n">
-        <v>7234175</v>
+        <v>7233786</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2761,22 +2666,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,57 +2701,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119934647</v>
+        <v>119934417</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>754937</v>
+        <v>755028</v>
       </c>
       <c r="R21" t="n">
-        <v>7234160</v>
+        <v>7233779</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2873,22 +2773,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,49 +2803,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119934331</v>
+        <v>119934418</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>755054</v>
+        <v>755018</v>
       </c>
       <c r="R22" t="n">
-        <v>7233787</v>
+        <v>7233765</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,54 +2922,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119934490</v>
+        <v>119934420</v>
       </c>
       <c r="B23" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>754837</v>
+        <v>755005</v>
       </c>
       <c r="R23" t="n">
-        <v>7233939</v>
+        <v>7233739</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3101,22 +2987,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3131,27 +3017,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119934168</v>
+        <v>119934423</v>
       </c>
       <c r="B24" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3183,7 +3064,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>755008</v>
+        <v>755006</v>
       </c>
       <c r="R24" t="n">
         <v>7233852</v>
@@ -3255,15 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119934165</v>
+        <v>119934425</v>
       </c>
       <c r="B25" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3295,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>755005</v>
+        <v>755043</v>
       </c>
       <c r="R25" t="n">
-        <v>7233743</v>
+        <v>7233898</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3330,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3340,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3367,37 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119934050</v>
+        <v>119934466</v>
       </c>
       <c r="B26" t="n">
-        <v>90084</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3407,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>754878</v>
+        <v>755018</v>
       </c>
       <c r="R26" t="n">
-        <v>7234190</v>
+        <v>7233889</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3442,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3452,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3479,37 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119934540</v>
+        <v>119934467</v>
       </c>
       <c r="B27" t="n">
-        <v>96891</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3519,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>754917</v>
+        <v>754901</v>
       </c>
       <c r="R27" t="n">
-        <v>7234139</v>
+        <v>7234127</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3554,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3579,49 +3445,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119934356</v>
+        <v>119934468</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3631,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>754783</v>
+        <v>754926</v>
       </c>
       <c r="R28" t="n">
-        <v>7233998</v>
+        <v>7234175</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3666,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3676,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3703,37 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119934072</v>
+        <v>119934470</v>
       </c>
       <c r="B29" t="n">
-        <v>91862</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3743,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>754781</v>
+        <v>754899</v>
       </c>
       <c r="R29" t="n">
-        <v>7234011</v>
+        <v>7234223</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3778,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3788,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3815,37 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119934585</v>
+        <v>119934686</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3855,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>754988</v>
+        <v>755129</v>
       </c>
       <c r="R30" t="n">
-        <v>7233911</v>
+        <v>7234019</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3890,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,50 +3778,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119934342</v>
+        <v>119934687</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>754990</v>
+        <v>754873</v>
       </c>
       <c r="R31" t="n">
-        <v>7233874</v>
+        <v>7233929</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3997,22 +3843,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4027,31 +3873,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119934354</v>
+        <v>119934324</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4075,14 +3916,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Grundvattnet, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>755035</v>
+        <v>755204</v>
       </c>
       <c r="R32" t="n">
-        <v>7233873</v>
+        <v>7233716</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4109,22 +3950,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4144,22 +3985,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119934002</v>
+        <v>119934325</v>
       </c>
       <c r="B33" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4167,34 +4003,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Grundvattnet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>754955</v>
+        <v>755201</v>
       </c>
       <c r="R33" t="n">
-        <v>7233873</v>
+        <v>7233655</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,15 +4099,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119934687</v>
+        <v>119934331</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4279,34 +4110,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>754873</v>
+        <v>755054</v>
       </c>
       <c r="R34" t="n">
-        <v>7233929</v>
+        <v>7233787</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4333,22 +4164,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4363,27 +4194,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119934425</v>
+        <v>119934332</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4415,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>755043</v>
+        <v>755002</v>
       </c>
       <c r="R35" t="n">
-        <v>7233898</v>
+        <v>7233709</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4450,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4487,15 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119934535</v>
+        <v>119934333</v>
       </c>
       <c r="B36" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,34 +4324,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>754839</v>
+        <v>755006</v>
       </c>
       <c r="R36" t="n">
-        <v>7233912</v>
+        <v>7233705</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4557,22 +4378,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,27 +4408,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119934077</v>
+        <v>119934334</v>
       </c>
       <c r="B37" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4615,34 +4431,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>754977</v>
+        <v>755032</v>
       </c>
       <c r="R37" t="n">
-        <v>7233937</v>
+        <v>7233670</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4669,22 +4485,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4704,57 +4520,52 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119934235</v>
+        <v>119934336</v>
       </c>
       <c r="B38" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>755041</v>
+        <v>755044</v>
       </c>
       <c r="R38" t="n">
-        <v>7233837</v>
+        <v>7233662</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4781,22 +4592,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4816,22 +4627,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119934423</v>
+        <v>119934340</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4839,21 +4645,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4863,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>755006</v>
+        <v>754870</v>
       </c>
       <c r="R39" t="n">
-        <v>7233852</v>
+        <v>7233834</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4898,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4935,15 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119934578</v>
+        <v>119934341</v>
       </c>
       <c r="B40" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4951,34 +4752,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>755012</v>
+        <v>754823</v>
       </c>
       <c r="R40" t="n">
-        <v>7233916</v>
+        <v>7233881</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5005,22 +4806,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5035,31 +4836,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119934641</v>
+        <v>119934342</v>
       </c>
       <c r="B41" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5083,14 +4879,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>755042</v>
+        <v>754990</v>
       </c>
       <c r="R41" t="n">
-        <v>7233875</v>
+        <v>7233874</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5117,22 +4913,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5147,62 +4943,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119934204</v>
+        <v>119934354</v>
       </c>
       <c r="B42" t="n">
-        <v>89247</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>755015</v>
+        <v>755035</v>
       </c>
       <c r="R42" t="n">
-        <v>7233693</v>
+        <v>7233873</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5229,22 +5020,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5264,22 +5055,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119934008</v>
+        <v>119934355</v>
       </c>
       <c r="B43" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5287,21 +5073,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5311,10 +5097,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>754781</v>
+        <v>754788</v>
       </c>
       <c r="R43" t="n">
-        <v>7234011</v>
+        <v>7233985</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5346,7 +5132,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5356,7 +5142,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5383,15 +5169,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119934007</v>
+        <v>119934356</v>
       </c>
       <c r="B44" t="n">
-        <v>89650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5399,21 +5180,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5423,10 +5204,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>755018</v>
+        <v>754783</v>
       </c>
       <c r="R44" t="n">
-        <v>7233903</v>
+        <v>7233998</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5458,7 +5239,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5468,7 +5249,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5495,15 +5276,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119934060</v>
+        <v>119934357</v>
       </c>
       <c r="B45" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5511,21 +5287,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5535,10 +5311,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>754930</v>
+        <v>754863</v>
       </c>
       <c r="R45" t="n">
-        <v>7234168</v>
+        <v>7234125</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5570,7 +5346,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5580,7 +5356,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5607,19 +5383,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119934648</v>
+        <v>119934358</v>
       </c>
       <c r="B46" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5647,10 +5418,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>754931</v>
+        <v>754903</v>
       </c>
       <c r="R46" t="n">
-        <v>7234162</v>
+        <v>7234130</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5682,7 +5453,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5692,7 +5463,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5707,27 +5478,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119934417</v>
+        <v>119934360</v>
       </c>
       <c r="B47" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5735,34 +5501,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>755028</v>
+        <v>754927</v>
       </c>
       <c r="R47" t="n">
-        <v>7233779</v>
+        <v>7234172</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5789,22 +5555,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5824,22 +5590,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119934415</v>
+        <v>119934641</v>
       </c>
       <c r="B48" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5847,34 +5608,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>755030</v>
+        <v>755042</v>
       </c>
       <c r="R48" t="n">
-        <v>7233786</v>
+        <v>7233875</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5901,22 +5662,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5931,27 +5692,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119934418</v>
+        <v>119934642</v>
       </c>
       <c r="B49" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5959,34 +5715,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>755018</v>
+        <v>755017</v>
       </c>
       <c r="R49" t="n">
-        <v>7233765</v>
+        <v>7233922</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6013,22 +5769,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6043,66 +5799,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119934489</v>
+        <v>119934643</v>
       </c>
       <c r="B50" t="n">
-        <v>56532</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>755029</v>
+        <v>754977</v>
       </c>
       <c r="R50" t="n">
-        <v>7233931</v>
+        <v>7233943</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6134,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6144,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6171,19 +5918,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119934358</v>
+        <v>119934644</v>
       </c>
       <c r="B51" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6211,10 +5953,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>754903</v>
+        <v>754960</v>
       </c>
       <c r="R51" t="n">
-        <v>7234130</v>
+        <v>7233931</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6246,7 +5988,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6256,7 +5998,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6271,27 +6013,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119934521</v>
+        <v>119934645</v>
       </c>
       <c r="B52" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6299,21 +6036,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6323,10 +6060,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>754884</v>
+        <v>754862</v>
       </c>
       <c r="R52" t="n">
-        <v>7234192</v>
+        <v>7234127</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6358,7 +6095,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6368,7 +6105,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6395,15 +6132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119934183</v>
+        <v>119934647</v>
       </c>
       <c r="B53" t="n">
-        <v>92048</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6411,34 +6143,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>754960</v>
+        <v>754937</v>
       </c>
       <c r="R53" t="n">
-        <v>7233858</v>
+        <v>7234160</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6465,22 +6197,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6495,62 +6227,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119933994</v>
+        <v>119934648</v>
       </c>
       <c r="B54" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>754913</v>
+        <v>754931</v>
       </c>
       <c r="R54" t="n">
-        <v>7233788</v>
+        <v>7234162</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6577,22 +6304,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6607,27 +6334,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119934237</v>
+        <v>119934072</v>
       </c>
       <c r="B55" t="n">
-        <v>89269</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6635,21 +6357,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6659,10 +6381,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>755046</v>
+        <v>754781</v>
       </c>
       <c r="R55" t="n">
-        <v>7233843</v>
+        <v>7234011</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6694,7 +6416,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6704,7 +6426,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6731,15 +6453,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119934466</v>
+        <v>119934044</v>
       </c>
       <c r="B56" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6747,21 +6464,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6771,10 +6488,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>755018</v>
+        <v>754873</v>
       </c>
       <c r="R56" t="n">
-        <v>7233889</v>
+        <v>7234247</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6806,7 +6523,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6816,7 +6533,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6843,15 +6560,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119934642</v>
+        <v>119933994</v>
       </c>
       <c r="B57" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6859,34 +6571,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Långtjärnen, Vb</t>
+          <t>Skravelbäcken, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>755017</v>
+        <v>754913</v>
       </c>
       <c r="R57" t="n">
-        <v>7233922</v>
+        <v>7233788</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6913,22 +6625,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6943,62 +6655,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Forsström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119934340</v>
+        <v>119934235</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>754870</v>
+        <v>755041</v>
       </c>
       <c r="R58" t="n">
-        <v>7233834</v>
+        <v>7233837</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7025,22 +6732,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7060,57 +6767,52 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119934420</v>
+        <v>119934237</v>
       </c>
       <c r="B59" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Skravelbäcken, Vb</t>
+          <t>Långtjärnen, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>755005</v>
+        <v>755046</v>
       </c>
       <c r="R59" t="n">
-        <v>7233739</v>
+        <v>7233843</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7137,22 +6839,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7172,10 +6874,660 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>119934489</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>755029</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7233931</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>119934490</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>754837</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7233939</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>119934585</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>754988</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7233911</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>119934540</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>754917</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7234139</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>119934049</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>754837</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7233966</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr"/>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>119934050</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Långtjärnen, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>754878</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7234190</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36807-2025 artfynd.xlsx
+++ b/artfynd/A 36807-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934219</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934204</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119933999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934002</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934003</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934535</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934183</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934160</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934163</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934165</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934168</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934580</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934581</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934415</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934417</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934418</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934420</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934423</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934425</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934466</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934467</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934468</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934470</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934686</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934687</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934324</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934325</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934331</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934332</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934333</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934334</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934336</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934340</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934341</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934342</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934354</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934355</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934356</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934357</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934358</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934360</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934641</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934642</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934643</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934644</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934645</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934647</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934648</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934072</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934044</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119933994</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934235</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934237</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6989,6 +7284,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934489</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7100,6 +7400,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934490</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7207,6 +7512,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934585</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7314,6 +7624,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934540</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7421,6 +7736,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934049</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7528,8 +7848,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934050</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>